--- a/output/pdf_financials_xlsx/VAU.xlsx
+++ b/output/pdf_financials_xlsx/VAU.xlsx
@@ -5613,16 +5613,16 @@
         <v>0.066508</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.066508</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.099841</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.099841</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.099841</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -15120,7 +15120,11 @@
           <t>Share-Based Payment Reserve 9</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16952,7 +16956,11 @@
           <t>Share-Based Payment Reserve 99,841</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -18494,7 +18502,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VAU.xlsx
+++ b/output/pdf_financials_xlsx/VAU.xlsx
@@ -1031,28 +1031,28 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00013</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.018789</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.016031</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.013955</v>
       </c>
     </row>
     <row r="13">
@@ -1926,28 +1926,28 @@
         <v>-0.22693</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.612501</v>
+        <v>-0.612541</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.81026</v>
+        <v>-1.810302</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.257097</v>
+        <v>-2.257227</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.601195</v>
+        <v>-2.60129</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.833242</v>
+        <v>-3.833266</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.769518</v>
+        <v>-3.788307</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.433477</v>
+        <v>-2.449508</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.608627</v>
+        <v>-2.622582</v>
       </c>
     </row>
     <row r="28">
@@ -2036,28 +2036,28 @@
         <v>-0.22693</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.612501</v>
+        <v>-0.612541</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.81026</v>
+        <v>-1.810302</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.257097</v>
+        <v>-2.257227</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.601195</v>
+        <v>-2.60129</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.833242</v>
+        <v>-3.833266</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.769518</v>
+        <v>-3.788307</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.433477</v>
+        <v>-2.449508</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.582021</v>
+        <v>-2.595976</v>
       </c>
     </row>
     <row r="30">
@@ -2315,7 +2315,7 @@
         <v>0.0629</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.0629</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.001281</v>
@@ -2345,10 +2345,10 @@
         <v>0.22265</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.33682</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.757767</v>
       </c>
     </row>
     <row r="35">
@@ -2425,7 +2425,7 @@
         <v>0.0629</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.0629</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.001281</v>
@@ -2455,10 +2455,10 @@
         <v>0.22265</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.33682</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.757767</v>
       </c>
     </row>
     <row r="37">
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.001865</v>
@@ -3115,10 +3115,10 @@
         <v>0.054567</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.426769</v>
+        <v>0.089949</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.836506</v>
+        <v>0.078739</v>
       </c>
     </row>
     <row r="49">
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005116</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005116</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -23908,7 +23908,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -33586,7 +33590,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -36160,7 +36164,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -41954,7 +41958,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -42052,7 +42056,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -42626,7 +42630,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -45966,7 +45970,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">

--- a/output/pdf_financials_xlsx/VAU.xlsx
+++ b/output/pdf_financials_xlsx/VAU.xlsx
@@ -765,7 +765,7 @@
         <v>0.107669</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.120543</v>
+        <v>0.150265</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.334911</v>
@@ -4030,10 +4030,10 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.01266</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.068507</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.057185</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
@@ -6072,16 +6072,16 @@
         <v>0.006566</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000427</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001225</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001765</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.00363</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0</v>
@@ -6102,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001251</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.001263</v>
       </c>
     </row>
     <row r="102">
@@ -6356,7 +6356,7 @@
         <v>0.004555</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.115033</v>
+        <v>-0.111403</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>-0.028645</v>
@@ -6377,10 +6377,10 @@
         <v>-0.727447</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.168226</v>
+        <v>-0.169477</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.114274</v>
+        <v>-0.113011</v>
       </c>
     </row>
     <row r="107">
@@ -20140,7 +20140,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -27256,7 +27260,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -27446,7 +27454,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -28892,7 +28904,11 @@
           <t>GST Recoverable</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -29174,7 +29190,11 @@
           <t>Proceeds from Share Issuance</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -39596,7 +39616,11 @@
           <t>Director fees 7</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
